--- a/sheets/대금율보/검수/당악.xlsx
+++ b/sheets/대금율보/검수/당악.xlsx
@@ -6787,8 +6787,7 @@
       <c r="G10" s="22"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I10" s="22"/>
@@ -6820,8 +6819,7 @@
       <c r="Q10" s="22"/>
       <c r="R10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="S10" s="22"/>
@@ -7081,8 +7079,7 @@
       <c r="M14" s="22"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="O14" s="22"/>
@@ -7366,8 +7363,7 @@
       <c r="Q18" s="22"/>
       <c r="R18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="S18" s="22"/>
@@ -7509,11 +7505,7 @@
       <c r="Q24" s="22"/>
       <c r="R24" s="21"/>
       <c r="S24" s="22"/>
-      <c r="T24" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T24" s="23"/>
       <c r="U24" s="24"/>
     </row>
     <row r="25" ht="56" customHeight="1">
@@ -7627,8 +7619,7 @@
         <is>
           <t xml:space="preserve">潢
 仲
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="U28" s="22"/>
@@ -7715,8 +7706,7 @@
         <is>
           <t xml:space="preserve">㳞
 –汰
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="U31" s="22"/>

--- a/sheets/대금율보/검수/당악.xlsx
+++ b/sheets/대금율보/검수/당악.xlsx
@@ -6186,32 +6186,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="11.63" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="11.63" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="11.63" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="11.63" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.63" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="11.63" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="11.63" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="11.63" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="11.63" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="11.63" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="86.96" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="97.23" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="97.23" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="97.23" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="97.23" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="97.23" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="97.23" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="U8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="97.23" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="97.23" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="U10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="97.23" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
       <c r="T11" s="21"/>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="97.23" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
       <c r="T12" s="21"/>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="97.23" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="97.23" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
       <c r="T14" s="21"/>
       <c r="U14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="97.23" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
       <c r="T15" s="21"/>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="97.23" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="22"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="97.23" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="97.23" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="22"/>
@@ -7370,10 +7370,10 @@
       <c r="T18" s="21"/>
       <c r="U18" s="22"/>
     </row>
-    <row r="19">
+    <row r="19" ht="6.0" customHeight="true">
       <c r="A19" s="0"/>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="86.96" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="20" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
       <c r="T20" s="20"/>
       <c r="U20" s="20"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="97.23" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -7427,7 +7427,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="97.23" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="22"/>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="U22" s="22"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="97.23" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="97.23" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="22"/>
@@ -7508,7 +7508,7 @@
       <c r="T24" s="23"/>
       <c r="U24" s="24"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="97.23" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="97.23" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="U26" s="22"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="97.23" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="22"/>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="U27" s="22"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="97.23" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="22"/>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="U28" s="22"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="97.23" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="U29" s="22"/>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="97.23" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="22"/>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="U30" s="22"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="97.23" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="22"/>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="U31" s="22"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="97.23" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="22"/>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="U32" s="22"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="97.23" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="97.23" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="22"/>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="U34" s="22"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="97.23" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="22"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="U35" s="22"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="97.23" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="22"/>
@@ -7861,7 +7861,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="18" max="16383" man="1"/>
   </rowBreaks>
